--- a/data/analysis/composite_evaluations.xlsx
+++ b/data/analysis/composite_evaluations.xlsx
@@ -492,18 +492,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
@@ -529,63 +529,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>11_WAQAS_AMIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ahmed Naeem</t>
+          <t>Waqas Amin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01_MUHAMMAD_SALMAN</t>
+          <t>13_MANZOOR_ELLAHI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -594,7 +594,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -604,29 +604,29 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MUHAMMAD SALMAN</t>
+          <t>Manzoor Ellahi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11_WAQAS_AMIN</t>
+          <t>23_WAQAS_TARIQ_TOOR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -635,7 +635,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -645,29 +645,29 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Waqas Amin</t>
+          <t>Waqas Tariq Toor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>43_AMMARA_NASIM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -676,7 +676,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -686,70 +686,70 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SYED TAMOORULHASSAN</t>
+          <t>Ammara Nasim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13_MANZOOR_ELLAHI</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Manzoor Ellahi</t>
+          <t>Ahmed Naeem</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14_SAROSH_TAHIR</t>
+          <t>09_MUHAMMAD_ABUBAKAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>80.7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -758,39 +758,39 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sarosh Tahir</t>
+          <t>Muhammad Abubakar</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>37_SANIA_GUL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>79.2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -799,39 +799,39 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="n">
         <v>15</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Muzzamil Ghaffar</t>
+          <t>Sania Gul</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23_WAQAS_TARIQ_TOOR</t>
+          <t>34_SHAHZAD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>78.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -840,39 +840,39 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Waqas Tariq Toor</t>
+          <t>Shahzad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>14_SAROSH_TAHIR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -881,7 +881,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
@@ -891,29 +891,29 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Qaisar Hussain Alvi</t>
+          <t>Sarosh Tahir</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>43_AMMARA_NASIM</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -922,39 +922,39 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ammara Nasim</t>
+          <t>Muhammad Aqeel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07_FIZA_MURTAZA</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>44.5</v>
+        <v>76.7</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -963,39 +963,39 @@
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Fiza Murtaza</t>
+          <t>Muhammad Amjad</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>01_MUHAMMAD_SALMAN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44.5</v>
+        <v>75</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1004,39 +1004,39 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
         <v>15</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>M. Usman Abbasi</t>
+          <t>MUHAMMAD SALMAN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19_ASIM_MASOOD</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44.5</v>
+        <v>75</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1045,39 +1045,39 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
         <v>15</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Asim Masood</t>
+          <t>Muzzamil Ghaffar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>44.5</v>
+        <v>75</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -1086,39 +1086,39 @@
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Aamina Akbar</t>
+          <t>Qaisar Hussain Alvi</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>37_SANIA_GUL</t>
+          <t>07_FIZA_MURTAZA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.5</v>
+        <v>74.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
         <v>7.5</v>
@@ -1137,70 +1137,70 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Sania Gul</t>
+          <t>Fiza Murtaza</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08_TAYYABA_GULL</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tayyaba Gull</t>
+          <t>Suhail Asghar Qureshi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09_MUHAMMAD_ABUBAKAR</t>
+          <t>03_NASIR_ALI_SHAH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>44</v>
+        <v>73.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1209,39 +1209,39 @@
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Muhammad Abubakar</t>
+          <t>Nasir Ali Shah</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>19_ASIM_MASOOD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>2</v>
@@ -1250,39 +1250,39 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Muhammad Amjad</t>
+          <t>Asim Masood</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
@@ -1291,80 +1291,80 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Saman Fatima</t>
+          <t>M. Usman Abbasi</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
+        <v>22</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" t="n">
-        <v>12</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Fahd Sikandar Khan</t>
+          <t>Zeeshan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>41.5</v>
+        <v>69</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1373,39 +1373,39 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
         <v>12</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Qamar Abbas</t>
+          <t>Fahd Sikandar Khan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>34_SHAHZAD</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41.5</v>
+        <v>68.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1414,39 +1414,39 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
         <v>7.5</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Shahzad</t>
+          <t>Aamina Akbar</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03_NASIR_ALI_SHAH</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1455,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -1465,29 +1465,29 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Nasir Ali Shah</t>
+          <t>Syed Fasih Ali</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -1496,39 +1496,39 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="n">
         <v>3</v>
       </c>
-      <c r="I26" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" t="n">
-        <v>8</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Syed Fasih Ali</t>
+          <t>Muhammad Saqib</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -1537,80 +1537,80 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="I27" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>8</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Abdur Rehman</t>
+          <t>Idris Khan</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n">
         <v>5</v>
       </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" t="n">
-        <v>10</v>
-      </c>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Muhammad Aqeel</t>
+          <t>Samana Batool</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>08_TAYYABA_GULL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.5</v>
+        <v>66.8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -1619,39 +1619,39 @@
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Farman Ali</t>
+          <t>Tayyaba Gull</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
@@ -1660,80 +1660,80 @@
         <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Shaheer</t>
+          <t>Muhammad Musadiq Ahmed</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.5</v>
+        <v>65</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
         <v>5</v>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Saqib Jamil</t>
+          <t>Muhammad Sarmad Tariq</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
@@ -1742,39 +1742,39 @@
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Samana Batool</t>
+          <t>Abdur Rehman</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>37.5</v>
+        <v>63.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -1783,39 +1783,39 @@
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Matiullah Ahsan</t>
+          <t>SYED TAMOORULHASSAN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36.5</v>
+        <v>63</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
@@ -1824,39 +1824,39 @@
         <v>2</v>
       </c>
       <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="I34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>12</v>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Muhammad Ehatisham</t>
+          <t>Usman Masud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -1865,39 +1865,39 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Suhail Asghar Qureshi</t>
+          <t>Qamar Abbas</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>36</v>
+        <v>61.5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -1906,80 +1906,80 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Zeeshan</t>
+          <t>Matiullah Ahsan</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
+        <v>16</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" t="n">
         <v>5</v>
       </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10</v>
-      </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Idris Khan</t>
+          <t>MUHAMMAD ADEEL ALTAF</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>36</v>
+        <v>54.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -1988,28 +1988,28 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I38" t="n">
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Muhammad Sarmad Tariq</t>
+          <t>Saman Fatima</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>36</v>
+        <v>48.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
         <v>5</v>
@@ -2029,28 +2029,28 @@
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Usman Masud</t>
+          <t>Shaheer</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>05_MUHAMMAD_MAJID</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>45.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2058,40 +2058,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>3</v>
-      </c>
-      <c r="I40" t="n">
-        <v>10</v>
-      </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Muhammad Saqib</t>
+          <t>MUHAMMAD MAJID</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05_MUHAMMAD_MAJID</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35</v>
+        <v>44.5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
         <v>5</v>
@@ -2111,28 +2111,28 @@
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>MUHAMMAD MAJID</t>
+          <t>Farman Ali</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>42_SAQIB_JAMIL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>35</v>
+        <v>44.5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
         <v>5</v>
@@ -2152,28 +2152,28 @@
         <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>MUHAMMAD ADEEL ALTAF</t>
+          <t>Saqib Jamil</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33.5</v>
+        <v>41.5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
         <v>5</v>
@@ -2193,17 +2193,17 @@
         <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Muhammad Musadiq Ahmed</t>
+          <t>Muhammad Ehatisham</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.5</v>
+        <v>32.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E44" t="n">
         <v>5</v>
@@ -2234,13 +2234,13 @@
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>2.5</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>

--- a/data/analysis/composite_evaluations.xlsx
+++ b/data/analysis/composite_evaluations.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>8</v>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>8</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80.7</v>
+        <v>83.7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.2</v>
+        <v>82.2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tier 2: Strong Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -793,7 +793,7 @@
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -820,11 +820,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78.5</v>
+        <v>81.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tier 2: Strong Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -834,7 +834,7 @@
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -861,11 +861,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tier 2: Strong Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -875,7 +875,7 @@
         <v>22</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tier 2: Strong Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -916,7 +916,7 @@
         <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76.7</v>
+        <v>79.7</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.5</v>
+        <v>77.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>73.5</v>
+        <v>76.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>22</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68.5</v>
+        <v>71.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>67.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66.8</v>
+        <v>69.8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>66.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1722,11 +1722,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.5</v>
+        <v>66.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1777,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -1804,11 +1804,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -1845,11 +1845,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1859,7 +1859,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>61.5</v>
+        <v>64.5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>16</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>54.5</v>
+        <v>57.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
@@ -2009,11 +2009,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2023,7 +2023,7 @@
         <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.5</v>
+        <v>44.5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>

--- a/data/analysis/composite_evaluations.xlsx
+++ b/data/analysis/composite_evaluations.xlsx
@@ -652,11 +652,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>43_AMMARA_NASIM</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -664,16 +664,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>10</v>
@@ -682,22 +682,22 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ammara Nasim</t>
+          <t>Ahmed Naeem</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>09_MUHAMMAD_ABUBAKAR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>83.7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -727,18 +727,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ahmed Naeem</t>
+          <t>Muhammad Abubakar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09_MUHAMMAD_ABUBAKAR</t>
+          <t>43_AMMARA_NASIM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.7</v>
+        <v>83</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
@@ -758,17 +758,17 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Muhammad Abubakar</t>
+          <t>Ammara Nasim</t>
         </is>
       </c>
     </row>
@@ -898,15 +898,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tier 1: Exceptional Fit</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -922,28 +922,28 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Muhammad Aqeel</t>
+          <t>Muhammad Amjad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>01_MUHAMMAD_SALMAN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.7</v>
+        <v>78</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -963,24 +963,24 @@
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Muhammad Amjad</t>
+          <t>MUHAMMAD SALMAN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01_MUHAMMAD_SALMAN</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1014,14 +1014,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>MUHAMMAD SALMAN</t>
+          <t>Muzzamil Ghaffar</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1055,18 +1055,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Muzzamil Ghaffar</t>
+          <t>Qaisar Hussain Alvi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>07_FIZA_MURTAZA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -1089,25 +1089,25 @@
         <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Qaisar Hussain Alvi</t>
+          <t>Fiza Murtaza</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07_FIZA_MURTAZA</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77.5</v>
+        <v>77</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -1130,25 +1130,25 @@
         <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Fiza Murtaza</t>
+          <t>Suhail Asghar Qureshi</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>03_NASIR_ALI_SHAH</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>77</v>
+        <v>76.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -1168,28 +1168,28 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I18" t="n">
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Suhail Asghar Qureshi</t>
+          <t>Nasir Ali Shah</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03_NASIR_ALI_SHAH</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>76.5</v>
+        <v>76</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -1209,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Nasir Ali Shah</t>
+          <t>Muhammad Aqeel</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1291,28 +1291,28 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>M. Usman Abbasi</t>
+          <t>Zeeshan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -1332,28 +1332,28 @@
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Zeeshan</t>
+          <t>Fahd Sikandar Khan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
@@ -1373,28 +1373,28 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Fahd Sikandar Khan</t>
+          <t>Aamina Akbar</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>71.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -1414,28 +1414,28 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Aamina Akbar</t>
+          <t>Muhammad Saqib</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -1455,28 +1455,28 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Syed Fasih Ali</t>
+          <t>M. Usman Abbasi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>70.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -1496,7 +1496,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
@@ -1506,18 +1506,18 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Muhammad Saqib</t>
+          <t>Idris Khan</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>08_TAYYABA_GULL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -1537,28 +1537,28 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Idris Khan</t>
+          <t>Tayyaba Gull</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1581,25 +1581,25 @@
         <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Samana Batool</t>
+          <t>Muhammad Sarmad Tariq</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08_TAYYABA_GULL</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69.8</v>
+        <v>67</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1619,28 +1619,28 @@
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Tayyaba Gull</t>
+          <t>Syed Fasih Ali</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -1660,28 +1660,28 @@
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Muhammad Musadiq Ahmed</t>
+          <t>Abdur Rehman</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68</v>
+        <v>66.5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
@@ -1701,28 +1701,28 @@
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Muhammad Sarmad Tariq</t>
+          <t>SYED TAMOORULHASSAN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
         <v>16</v>
@@ -1745,25 +1745,25 @@
         <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>8</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Abdur Rehman</t>
+          <t>MUHAMMAD ADEEL ALTAF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66.5</v>
+        <v>66</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
         <v>16</v>
@@ -1783,24 +1783,24 @@
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SYED TAMOORULHASSAN</t>
+          <t>Usman Masud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
         <v>16</v>
@@ -1827,25 +1827,25 @@
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Usman Masud</t>
+          <t>Samana Batool</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -1865,17 +1865,17 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5</v>
+        <v>9.9</v>
       </c>
       <c r="I35" t="n">
         <v>7.5</v>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Qamar Abbas</t>
+          <t>Muhammad Musadiq Ahmed</t>
         </is>
       </c>
     </row>
@@ -1923,11 +1923,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62</v>
+        <v>57.5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -1947,28 +1947,28 @@
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>MUHAMMAD ADEEL ALTAF</t>
+          <t>Saman Fatima</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -1991,25 +1991,25 @@
         <v>2.5</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J38" t="n">
         <v>12</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Saman Fatima</t>
+          <t>Qamar Abbas</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>05_MUHAMMAD_MAJID</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
         <v>5</v>
@@ -2029,28 +2029,28 @@
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Shaheer</t>
+          <t>MUHAMMAD MAJID</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05_MUHAMMAD_MAJID</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
@@ -2070,24 +2070,24 @@
         <v>2</v>
       </c>
       <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
         <v>2.5</v>
       </c>
-      <c r="I40" t="n">
-        <v>5</v>
-      </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MUHAMMAD MAJID</t>
+          <t>Farman Ali</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Farman Ali</t>
+          <t>Muhammad Ehatisham</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2162,18 +2162,18 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Saqib Jamil</t>
+          <t>Shaheer</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>42_SAQIB_JAMIL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2199,11 +2199,11 @@
         <v>2.5</v>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Muhammad Ehatisham</t>
+          <t>Saqib Jamil</t>
         </is>
       </c>
     </row>

--- a/data/analysis/composite_evaluations.xlsx
+++ b/data/analysis/composite_evaluations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,11 +652,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>43_AMMARA_NASIM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -664,16 +664,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>10</v>
@@ -682,22 +682,22 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ahmed Naeem</t>
+          <t>Ammara Nasim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09_MUHAMMAD_ABUBAKAR</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.7</v>
+        <v>85</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -727,18 +727,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Muhammad Abubakar</t>
+          <t>Ahmed Naeem</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43_AMMARA_NASIM</t>
+          <t>09_MUHAMMAD_ABUBAKAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>83.7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
@@ -758,17 +758,17 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ammara Nasim</t>
+          <t>Muhammad Abubakar</t>
         </is>
       </c>
     </row>
@@ -898,15 +898,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tier 2: Strong Candidate</t>
+          <t>Tier 1: Exceptional Fit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -922,28 +922,28 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Muhammad Amjad</t>
+          <t>Muhammad Aqeel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01_MUHAMMAD_SALMAN</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -963,24 +963,24 @@
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="I13" t="n">
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>MUHAMMAD SALMAN</t>
+          <t>Muhammad Amjad</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>01_MUHAMMAD_SALMAN</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1014,14 +1014,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Muzzamil Ghaffar</t>
+          <t>MUHAMMAD SALMAN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1055,18 +1055,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Qaisar Hussain Alvi</t>
+          <t>Muzzamil Ghaffar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07_FIZA_MURTAZA</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77.5</v>
+        <v>78</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -1089,25 +1089,25 @@
         <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Fiza Murtaza</t>
+          <t>Qaisar Hussain Alvi</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>07_FIZA_MURTAZA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77</v>
+        <v>77.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -1130,25 +1130,25 @@
         <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Suhail Asghar Qureshi</t>
+          <t>Fiza Murtaza</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03_NASIR_ALI_SHAH</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>76.5</v>
+        <v>77</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -1168,28 +1168,28 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Nasir Ali Shah</t>
+          <t>Suhail Asghar Qureshi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>03_NASIR_ALI_SHAH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -1209,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Muhammad Aqeel</t>
+          <t>Nasir Ali Shah</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1291,28 +1291,28 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Zeeshan</t>
+          <t>M. Usman Abbasi</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -1332,28 +1332,28 @@
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Fahd Sikandar Khan</t>
+          <t>Zeeshan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
@@ -1373,28 +1373,28 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Aamina Akbar</t>
+          <t>Fahd Sikandar Khan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -1414,28 +1414,28 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Muhammad Saqib</t>
+          <t>Aamina Akbar</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -1455,28 +1455,28 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>M. Usman Abbasi</t>
+          <t>Syed Fasih Ali</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>70</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -1496,7 +1496,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
@@ -1506,18 +1506,18 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Idris Khan</t>
+          <t>Muhammad Saqib</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08_TAYYABA_GULL</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -1537,28 +1537,28 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Tayyaba Gull</t>
+          <t>Idris Khan</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1581,25 +1581,25 @@
         <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Muhammad Sarmad Tariq</t>
+          <t>Samana Batool</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>08_TAYYABA_GULL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>67</v>
+        <v>69.8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1619,28 +1619,28 @@
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Syed Fasih Ali</t>
+          <t>Tayyaba Gull</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>67</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -1660,28 +1660,28 @@
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Abdur Rehman</t>
+          <t>Muhammad Musadiq Ahmed</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
@@ -1701,28 +1701,28 @@
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SYED TAMOORULHASSAN</t>
+          <t>Muhammad Sarmad Tariq</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
         <v>16</v>
@@ -1745,25 +1745,25 @@
         <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
         <v>8</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MUHAMMAD ADEEL ALTAF</t>
+          <t>Abdur Rehman</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
         <v>16</v>
@@ -1783,24 +1783,24 @@
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I33" t="n">
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Usman Masud</t>
+          <t>SYED TAMOORULHASSAN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>09_SANA_FATIMA_RIZVI</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1834,18 +1834,18 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Samana Batool</t>
+          <t>Sana Fatima Rizvi</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -1865,36 +1865,36 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Muhammad Musadiq Ahmed</t>
+          <t>Usman Masud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tier 3: Moderate Candidate</t>
+          <t>Tier 2: Strong Candidate</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E36" t="n">
         <v>16</v>
@@ -1906,28 +1906,28 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="I36" t="n">
         <v>7.5</v>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Matiullah Ahsan</t>
+          <t>Qamar Abbas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>57.5</v>
+        <v>64.5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -1947,28 +1947,28 @@
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Saman Fatima</t>
+          <t>Matiullah Ahsan</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
         <v>16</v>
@@ -1988,28 +1988,28 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Qamar Abbas</t>
+          <t>MUHAMMAD ADEEL ALTAF</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05_MUHAMMAD_MAJID</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2032,36 +2032,36 @@
         <v>2.5</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
         <v>12</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MUHAMMAD MAJID</t>
+          <t>Saman Fatima</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>05_MUHAMMAD_MAJID</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
@@ -2070,36 +2070,36 @@
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Farman Ali</t>
+          <t>MUHAMMAD MAJID</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>47.5</v>
+        <v>51.5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tier 4: Needs Clarification / Weak</t>
+          <t>Tier 3: Moderate Candidate</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E41" t="n">
         <v>5</v>
@@ -2121,14 +2121,14 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Muhammad Ehatisham</t>
+          <t>Shaheer</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2162,14 +2162,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Shaheer</t>
+          <t>Farman Ali</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2203,18 +2203,18 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Saqib Jamil</t>
+          <t>Muhammad Ehatisham</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>02_MUHAMMAD_SHAHWAZ</t>
+          <t>42_SAQIB_JAMIL</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>35.5</v>
+        <v>47.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
         <v>5</v>
@@ -2240,9 +2240,87 @@
         <v>2.5</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>Saqib Jamil</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tier 4: Needs Clarification / Weak</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>02_MUHAMMAD_SHAHWAZ</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tier 4: Needs Clarification / Weak</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>MUHAMMAD SHAHWAZ</t>
         </is>
